--- a/Upload/Draw.xlsx
+++ b/Upload/Draw.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\PHP_old\public\Upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\canbo\Desktop\Projects\SkySail-new\Upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E38585-5F5D-4388-AE26-635F75884F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81F5005-0536-4EC9-B8EB-ECA9670B3048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{C419D7EC-7614-48CE-A3F7-A99002D1B48F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30168" windowHeight="19464" xr2:uid="{C419D7EC-7614-48CE-A3F7-A99002D1B48F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$536</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$562</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="158">
   <si>
     <t>SINP</t>
   </si>
@@ -374,9 +374,6 @@
     <t>Foreign Skilled Worker Program nominees only</t>
   </si>
   <si>
-    <t>OINO</t>
-  </si>
-  <si>
     <t>Employer Job Offer: In-Demand Skills stream - Targeted draw for Central Ontario (excluding GTA)</t>
   </si>
   <si>
@@ -504,6 +501,15 @@
   </si>
   <si>
     <t>Employer Job Offer In-Demand Skills stream - agriculture-related and other priority occupations</t>
+  </si>
+  <si>
+    <t>French-Language proficiency</t>
+  </si>
+  <si>
+    <t>Skilled Military Recruits</t>
+  </si>
+  <si>
+    <t>Transport Occupations</t>
   </si>
 </sst>
 </file>
@@ -880,17 +886,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A0282E-C66F-47D3-9A9F-ADD17816EADE}">
-  <dimension ref="A1:E536"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E562"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="99.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -907,7 +913,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -924,7 +930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -941,7 +947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -958,7 +964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -975,7 +981,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -992,7 +998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1009,7 +1015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +1032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -1043,7 +1049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -1094,7 +1100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1111,7 +1117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1128,7 +1134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -1145,7 +1151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -1179,7 +1185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1213,7 +1219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -1230,7 +1236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1247,7 +1253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1281,7 +1287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1349,7 +1355,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1366,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1383,7 +1389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1400,7 +1406,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1417,7 +1423,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1451,7 +1457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1468,7 +1474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1485,7 +1491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -1553,7 +1559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1570,7 +1576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -1587,7 +1593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -1604,7 +1610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -1621,7 +1627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -1655,7 +1661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -1672,7 +1678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -1689,7 +1695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -1706,7 +1712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -1723,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -1740,7 +1746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -1757,7 +1763,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -1774,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -1791,7 +1797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1808,7 +1814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1825,7 +1831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -1842,7 +1848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -1859,7 +1865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1876,7 +1882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -1893,7 +1899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1910,7 +1916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1927,7 +1933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -1944,7 +1950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -1961,7 +1967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -1978,7 +1984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -1995,7 +2001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -2012,7 +2018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -2029,7 +2035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -2046,7 +2052,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2063,7 +2069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -2080,7 +2086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -2097,7 +2103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2114,7 +2120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2131,7 +2137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -2148,7 +2154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2165,7 +2171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2182,7 +2188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2199,7 +2205,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2233,7 +2239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -2250,7 +2256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -2267,7 +2273,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -2284,7 +2290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -2301,7 +2307,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -2318,7 +2324,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -2335,7 +2341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2352,7 +2358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -2369,7 +2375,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -2386,7 +2392,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -2403,7 +2409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -2420,7 +2426,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -2437,7 +2443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -2454,7 +2460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -2471,7 +2477,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>6</v>
       </c>
@@ -2488,7 +2494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2505,7 +2511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>6</v>
       </c>
@@ -2522,7 +2528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -2539,7 +2545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -2556,7 +2562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -2573,7 +2579,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>6</v>
       </c>
@@ -2590,7 +2596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -2607,7 +2613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -2624,7 +2630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>6</v>
       </c>
@@ -2641,7 +2647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -2658,7 +2664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -2675,7 +2681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>6</v>
       </c>
@@ -2692,7 +2698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>6</v>
       </c>
@@ -2709,7 +2715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>6</v>
       </c>
@@ -2726,7 +2732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -2743,7 +2749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -2760,7 +2766,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -2777,7 +2783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -2794,7 +2800,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -2811,7 +2817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -2828,7 +2834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>43</v>
       </c>
@@ -2845,7 +2851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>43</v>
       </c>
@@ -2862,7 +2868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>43</v>
       </c>
@@ -2879,7 +2885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>43</v>
       </c>
@@ -2896,7 +2902,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>43</v>
       </c>
@@ -2913,7 +2919,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>43</v>
       </c>
@@ -2930,7 +2936,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>43</v>
       </c>
@@ -2947,7 +2953,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>43</v>
       </c>
@@ -2964,7 +2970,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>43</v>
       </c>
@@ -2981,7 +2987,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>43</v>
       </c>
@@ -2998,7 +3004,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>43</v>
       </c>
@@ -3015,7 +3021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>43</v>
       </c>
@@ -3032,7 +3038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>43</v>
       </c>
@@ -3049,7 +3055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>43</v>
       </c>
@@ -3066,7 +3072,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>43</v>
       </c>
@@ -3083,7 +3089,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>43</v>
       </c>
@@ -3100,7 +3106,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>43</v>
       </c>
@@ -3117,7 +3123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>43</v>
       </c>
@@ -3134,7 +3140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>43</v>
       </c>
@@ -3151,7 +3157,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>43</v>
       </c>
@@ -3168,7 +3174,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>43</v>
       </c>
@@ -3185,7 +3191,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>43</v>
       </c>
@@ -3202,7 +3208,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>43</v>
       </c>
@@ -3219,7 +3225,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>43</v>
       </c>
@@ -3236,7 +3242,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>43</v>
       </c>
@@ -3253,7 +3259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>43</v>
       </c>
@@ -3270,7 +3276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>43</v>
       </c>
@@ -3287,7 +3293,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>43</v>
       </c>
@@ -3304,7 +3310,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>43</v>
       </c>
@@ -3321,7 +3327,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>43</v>
       </c>
@@ -3338,7 +3344,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>43</v>
       </c>
@@ -3355,7 +3361,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>43</v>
       </c>
@@ -3372,7 +3378,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>43</v>
       </c>
@@ -3389,7 +3395,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>43</v>
       </c>
@@ -3406,7 +3412,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>43</v>
       </c>
@@ -3423,7 +3429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>43</v>
       </c>
@@ -3440,7 +3446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>43</v>
       </c>
@@ -3457,7 +3463,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>43</v>
       </c>
@@ -3474,7 +3480,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>43</v>
       </c>
@@ -3491,7 +3497,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>43</v>
       </c>
@@ -3508,7 +3514,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>43</v>
       </c>
@@ -3525,7 +3531,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>43</v>
       </c>
@@ -3542,7 +3548,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>43</v>
       </c>
@@ -3559,7 +3565,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>43</v>
       </c>
@@ -3576,7 +3582,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>43</v>
       </c>
@@ -3593,7 +3599,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>43</v>
       </c>
@@ -3610,7 +3616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>43</v>
       </c>
@@ -3627,7 +3633,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>43</v>
       </c>
@@ -3644,7 +3650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>43</v>
       </c>
@@ -3661,7 +3667,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>43</v>
       </c>
@@ -3678,7 +3684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>43</v>
       </c>
@@ -3695,7 +3701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>43</v>
       </c>
@@ -3712,7 +3718,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>43</v>
       </c>
@@ -3729,7 +3735,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>43</v>
       </c>
@@ -3746,7 +3752,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>43</v>
       </c>
@@ -3763,7 +3769,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>43</v>
       </c>
@@ -3780,7 +3786,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>43</v>
       </c>
@@ -3797,7 +3803,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>43</v>
       </c>
@@ -3814,7 +3820,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>43</v>
       </c>
@@ -3831,7 +3837,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>43</v>
       </c>
@@ -3848,7 +3854,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>43</v>
       </c>
@@ -3865,7 +3871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>43</v>
       </c>
@@ -3882,7 +3888,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>43</v>
       </c>
@@ -3899,7 +3905,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>43</v>
       </c>
@@ -3916,7 +3922,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>43</v>
       </c>
@@ -3933,7 +3939,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>43</v>
       </c>
@@ -3950,7 +3956,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>43</v>
       </c>
@@ -3967,7 +3973,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>43</v>
       </c>
@@ -3984,7 +3990,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>43</v>
       </c>
@@ -4001,7 +4007,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>43</v>
       </c>
@@ -4018,7 +4024,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>43</v>
       </c>
@@ -4035,7 +4041,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>43</v>
       </c>
@@ -4052,7 +4058,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>43</v>
       </c>
@@ -4069,7 +4075,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>43</v>
       </c>
@@ -4086,7 +4092,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>43</v>
       </c>
@@ -4103,7 +4109,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>43</v>
       </c>
@@ -4120,7 +4126,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>43</v>
       </c>
@@ -4137,7 +4143,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>43</v>
       </c>
@@ -4154,7 +4160,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>43</v>
       </c>
@@ -4171,7 +4177,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>43</v>
       </c>
@@ -4188,7 +4194,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>43</v>
       </c>
@@ -4205,7 +4211,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>43</v>
       </c>
@@ -4222,7 +4228,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>43</v>
       </c>
@@ -4239,7 +4245,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>43</v>
       </c>
@@ -4256,7 +4262,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>43</v>
       </c>
@@ -4273,7 +4279,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>43</v>
       </c>
@@ -4290,7 +4296,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>43</v>
       </c>
@@ -4307,7 +4313,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>43</v>
       </c>
@@ -4324,7 +4330,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>43</v>
       </c>
@@ -4341,7 +4347,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>43</v>
       </c>
@@ -4358,7 +4364,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>43</v>
       </c>
@@ -4375,7 +4381,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>43</v>
       </c>
@@ -4392,7 +4398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>43</v>
       </c>
@@ -4409,7 +4415,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>43</v>
       </c>
@@ -4426,7 +4432,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>43</v>
       </c>
@@ -4443,7 +4449,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>43</v>
       </c>
@@ -4460,7 +4466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>43</v>
       </c>
@@ -4477,7 +4483,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>43</v>
       </c>
@@ -4494,7 +4500,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>43</v>
       </c>
@@ -4511,7 +4517,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>43</v>
       </c>
@@ -4528,7 +4534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>43</v>
       </c>
@@ -4545,7 +4551,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>43</v>
       </c>
@@ -4562,7 +4568,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>43</v>
       </c>
@@ -4579,7 +4585,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>43</v>
       </c>
@@ -4596,7 +4602,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>43</v>
       </c>
@@ -4613,7 +4619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>51</v>
       </c>
@@ -4630,7 +4636,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>51</v>
       </c>
@@ -4647,7 +4653,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>51</v>
       </c>
@@ -4664,7 +4670,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>51</v>
       </c>
@@ -4681,7 +4687,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>51</v>
       </c>
@@ -4698,7 +4704,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>51</v>
       </c>
@@ -4715,7 +4721,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>51</v>
       </c>
@@ -4732,7 +4738,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>51</v>
       </c>
@@ -4749,7 +4755,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>51</v>
       </c>
@@ -4766,7 +4772,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>51</v>
       </c>
@@ -4783,7 +4789,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>51</v>
       </c>
@@ -4800,7 +4806,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>51</v>
       </c>
@@ -4817,7 +4823,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>51</v>
       </c>
@@ -4834,7 +4840,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>51</v>
       </c>
@@ -4851,7 +4857,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>51</v>
       </c>
@@ -4868,7 +4874,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>51</v>
       </c>
@@ -4885,7 +4891,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>51</v>
       </c>
@@ -4902,7 +4908,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>51</v>
       </c>
@@ -4919,7 +4925,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>51</v>
       </c>
@@ -4936,7 +4942,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>51</v>
       </c>
@@ -4953,7 +4959,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>53</v>
       </c>
@@ -4967,10 +4973,10 @@
         <v>7</v>
       </c>
       <c r="E240" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>53</v>
       </c>
@@ -4987,7 +4993,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>53</v>
       </c>
@@ -5001,10 +5007,10 @@
         <v>25</v>
       </c>
       <c r="E242" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>53</v>
       </c>
@@ -5018,10 +5024,10 @@
         <v>46</v>
       </c>
       <c r="E243" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>53</v>
       </c>
@@ -5038,7 +5044,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>53</v>
       </c>
@@ -5052,10 +5058,10 @@
         <v>63</v>
       </c>
       <c r="E245" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>53</v>
       </c>
@@ -5069,10 +5075,10 @@
         <v>20</v>
       </c>
       <c r="E246" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>53</v>
       </c>
@@ -5089,7 +5095,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>53</v>
       </c>
@@ -5103,10 +5109,10 @@
         <v>35</v>
       </c>
       <c r="E248" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>53</v>
       </c>
@@ -5120,10 +5126,10 @@
         <v>43</v>
       </c>
       <c r="E249" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>53</v>
       </c>
@@ -5137,10 +5143,10 @@
         <v>34</v>
       </c>
       <c r="E250" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>53</v>
       </c>
@@ -5154,10 +5160,10 @@
         <v>85</v>
       </c>
       <c r="E251" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>53</v>
       </c>
@@ -5171,10 +5177,10 @@
         <v>56</v>
       </c>
       <c r="E252" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>53</v>
       </c>
@@ -5188,10 +5194,10 @@
         <v>32</v>
       </c>
       <c r="E253" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>53</v>
       </c>
@@ -5205,10 +5211,10 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>53</v>
       </c>
@@ -5222,10 +5228,10 @@
         <v>90</v>
       </c>
       <c r="E255" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>53</v>
       </c>
@@ -5239,10 +5245,10 @@
         <v>82</v>
       </c>
       <c r="E256" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>53</v>
       </c>
@@ -5256,10 +5262,10 @@
         <v>81</v>
       </c>
       <c r="E257" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>53</v>
       </c>
@@ -5273,10 +5279,10 @@
         <v>80</v>
       </c>
       <c r="E258" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>53</v>
       </c>
@@ -5290,10 +5296,10 @@
         <v>83</v>
       </c>
       <c r="E259" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>53</v>
       </c>
@@ -5307,10 +5313,10 @@
         <v>61</v>
       </c>
       <c r="E260" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>53</v>
       </c>
@@ -5324,10 +5330,10 @@
         <v>55</v>
       </c>
       <c r="E261" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>53</v>
       </c>
@@ -5341,10 +5347,10 @@
         <v>53</v>
       </c>
       <c r="E262" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>53</v>
       </c>
@@ -5358,10 +5364,10 @@
         <v>54</v>
       </c>
       <c r="E263" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>53</v>
       </c>
@@ -5375,10 +5381,10 @@
         <v>57</v>
       </c>
       <c r="E264" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>53</v>
       </c>
@@ -5392,10 +5398,10 @@
         <v>49</v>
       </c>
       <c r="E265" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>53</v>
       </c>
@@ -5409,10 +5415,10 @@
         <v>30</v>
       </c>
       <c r="E266" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>53</v>
       </c>
@@ -5429,7 +5435,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>53</v>
       </c>
@@ -5446,7 +5452,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>53</v>
       </c>
@@ -5460,10 +5466,10 @@
         <v>36</v>
       </c>
       <c r="E269" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>53</v>
       </c>
@@ -5477,10 +5483,10 @@
         <v>47</v>
       </c>
       <c r="E270" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>53</v>
       </c>
@@ -5494,10 +5500,10 @@
         <v>50</v>
       </c>
       <c r="E271" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>53</v>
       </c>
@@ -5511,10 +5517,10 @@
         <v>50</v>
       </c>
       <c r="E272" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>53</v>
       </c>
@@ -5528,10 +5534,10 @@
         <v>33</v>
       </c>
       <c r="E273" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>53</v>
       </c>
@@ -5548,7 +5554,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>53</v>
       </c>
@@ -5562,10 +5568,10 @@
         <v>7</v>
       </c>
       <c r="E275" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>53</v>
       </c>
@@ -5579,10 +5585,10 @@
         <v>80</v>
       </c>
       <c r="E276" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>53</v>
       </c>
@@ -5599,7 +5605,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>53</v>
       </c>
@@ -5613,10 +5619,10 @@
         <v>56</v>
       </c>
       <c r="E278" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>53</v>
       </c>
@@ -5630,10 +5636,10 @@
         <v>7</v>
       </c>
       <c r="E279" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>53</v>
       </c>
@@ -5647,10 +5653,10 @@
         <v>54</v>
       </c>
       <c r="E280" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>53</v>
       </c>
@@ -5664,10 +5670,10 @@
         <v>51</v>
       </c>
       <c r="E281" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>53</v>
       </c>
@@ -5681,10 +5687,10 @@
         <v>51</v>
       </c>
       <c r="E282" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>53</v>
       </c>
@@ -5698,10 +5704,10 @@
         <v>49</v>
       </c>
       <c r="E283" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>53</v>
       </c>
@@ -5715,10 +5721,10 @@
         <v>77</v>
       </c>
       <c r="E284" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>53</v>
       </c>
@@ -5732,10 +5738,10 @@
         <v>77</v>
       </c>
       <c r="E285" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>53</v>
       </c>
@@ -5749,10 +5755,10 @@
         <v>73</v>
       </c>
       <c r="E286" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>53</v>
       </c>
@@ -5766,10 +5772,10 @@
         <v>71</v>
       </c>
       <c r="E287" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>53</v>
       </c>
@@ -5783,10 +5789,10 @@
         <v>30</v>
       </c>
       <c r="E288" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>53</v>
       </c>
@@ -5800,10 +5806,10 @@
         <v>30</v>
       </c>
       <c r="E289" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>53</v>
       </c>
@@ -5820,7 +5826,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>53</v>
       </c>
@@ -5837,7 +5843,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>53</v>
       </c>
@@ -5854,7 +5860,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>53</v>
       </c>
@@ -5871,7 +5877,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>53</v>
       </c>
@@ -5888,7 +5894,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>53</v>
       </c>
@@ -5905,7 +5911,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>53</v>
       </c>
@@ -5922,7 +5928,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>53</v>
       </c>
@@ -5939,9 +5945,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="B298" s="1">
         <v>45939</v>
@@ -5956,9 +5962,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="B299" s="1">
         <v>45939</v>
@@ -5973,7 +5979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>53</v>
       </c>
@@ -5990,7 +5996,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>53</v>
       </c>
@@ -6007,7 +6013,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>53</v>
       </c>
@@ -6024,7 +6030,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>53</v>
       </c>
@@ -6041,7 +6047,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>53</v>
       </c>
@@ -6058,7 +6064,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>53</v>
       </c>
@@ -6075,7 +6081,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>53</v>
       </c>
@@ -6092,7 +6098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>53</v>
       </c>
@@ -6109,7 +6115,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>53</v>
       </c>
@@ -6126,7 +6132,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>53</v>
       </c>
@@ -6143,7 +6149,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>53</v>
       </c>
@@ -6160,7 +6166,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>53</v>
       </c>
@@ -6177,7 +6183,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>53</v>
       </c>
@@ -6194,7 +6200,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>53</v>
       </c>
@@ -6211,7 +6217,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>53</v>
       </c>
@@ -6228,7 +6234,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>53</v>
       </c>
@@ -6245,7 +6251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>53</v>
       </c>
@@ -6262,7 +6268,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>53</v>
       </c>
@@ -6279,7 +6285,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>53</v>
       </c>
@@ -6296,7 +6302,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>53</v>
       </c>
@@ -6313,7 +6319,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>53</v>
       </c>
@@ -6330,7 +6336,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>53</v>
       </c>
@@ -6347,7 +6353,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>53</v>
       </c>
@@ -6364,7 +6370,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>53</v>
       </c>
@@ -6381,7 +6387,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>53</v>
       </c>
@@ -6398,7 +6404,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>53</v>
       </c>
@@ -6415,7 +6421,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>53</v>
       </c>
@@ -6432,7 +6438,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>53</v>
       </c>
@@ -6449,7 +6455,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>53</v>
       </c>
@@ -6466,7 +6472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>53</v>
       </c>
@@ -6483,7 +6489,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>53</v>
       </c>
@@ -6500,7 +6506,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>53</v>
       </c>
@@ -6517,7 +6523,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>53</v>
       </c>
@@ -6534,7 +6540,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>53</v>
       </c>
@@ -6551,7 +6557,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>53</v>
       </c>
@@ -6568,7 +6574,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>53</v>
       </c>
@@ -6585,7 +6591,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>53</v>
       </c>
@@ -6602,7 +6608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>53</v>
       </c>
@@ -6619,7 +6625,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>53</v>
       </c>
@@ -6636,7 +6642,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>53</v>
       </c>
@@ -6653,7 +6659,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>53</v>
       </c>
@@ -6670,7 +6676,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>53</v>
       </c>
@@ -6687,7 +6693,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>53</v>
       </c>
@@ -6704,7 +6710,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>53</v>
       </c>
@@ -6721,7 +6727,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>53</v>
       </c>
@@ -6738,7 +6744,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>53</v>
       </c>
@@ -6755,7 +6761,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>53</v>
       </c>
@@ -6772,7 +6778,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>53</v>
       </c>
@@ -6789,7 +6795,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>53</v>
       </c>
@@ -6806,7 +6812,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>53</v>
       </c>
@@ -6823,7 +6829,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>53</v>
       </c>
@@ -6840,7 +6846,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>53</v>
       </c>
@@ -6857,7 +6863,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>53</v>
       </c>
@@ -6874,7 +6880,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>53</v>
       </c>
@@ -6891,7 +6897,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>53</v>
       </c>
@@ -6908,7 +6914,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>53</v>
       </c>
@@ -6925,7 +6931,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>53</v>
       </c>
@@ -6942,7 +6948,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>53</v>
       </c>
@@ -6959,7 +6965,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>53</v>
       </c>
@@ -6976,7 +6982,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>53</v>
       </c>
@@ -6993,7 +6999,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>53</v>
       </c>
@@ -7010,7 +7016,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>53</v>
       </c>
@@ -7027,2983 +7033,3425 @@
         <v>85</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>88</v>
       </c>
       <c r="B362" s="1">
-        <v>46127</v>
+        <v>46253</v>
       </c>
       <c r="C362">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="D362">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="E362" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>88</v>
       </c>
       <c r="B363" s="1">
-        <v>46126</v>
+        <v>46252</v>
       </c>
       <c r="C363">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D363">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E363" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>88</v>
       </c>
       <c r="B364" s="1">
-        <v>46125</v>
+        <v>46251</v>
       </c>
       <c r="C364">
-        <v>324</v>
+        <v>442</v>
       </c>
       <c r="D364">
-        <v>786</v>
+        <v>760</v>
       </c>
       <c r="E364" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>88</v>
       </c>
       <c r="B365" s="1">
-        <v>46114</v>
+        <v>46241</v>
       </c>
       <c r="C365">
+        <v>300</v>
+      </c>
+      <c r="D365">
+        <v>470</v>
+      </c>
+      <c r="E365" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>88</v>
+      </c>
+      <c r="B366" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C366">
+        <v>5000</v>
+      </c>
+      <c r="D366">
+        <v>391</v>
+      </c>
+      <c r="E366" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>88</v>
+      </c>
+      <c r="B367" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C367">
         <v>3000</v>
       </c>
-      <c r="D365">
-        <v>477</v>
-      </c>
-      <c r="E365" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A366" t="s">
-        <v>88</v>
-      </c>
-      <c r="B366" s="1">
-        <v>46112</v>
-      </c>
-      <c r="C366">
-        <v>2250</v>
-      </c>
-      <c r="D366">
-        <v>509</v>
-      </c>
-      <c r="E366" t="s">
+      <c r="D367">
+        <v>516</v>
+      </c>
+      <c r="E367" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A367" t="s">
-        <v>88</v>
-      </c>
-      <c r="B367" s="1">
-        <v>46111</v>
-      </c>
-      <c r="C367">
-        <v>356</v>
-      </c>
-      <c r="D367">
-        <v>802</v>
-      </c>
-      <c r="E367" t="s">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>88</v>
+      </c>
+      <c r="B368" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C368">
+        <v>507</v>
+      </c>
+      <c r="D368">
+        <v>768</v>
+      </c>
+      <c r="E368" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A368" t="s">
-        <v>88</v>
-      </c>
-      <c r="B368" s="1">
-        <v>46099</v>
-      </c>
-      <c r="C368">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>88</v>
+      </c>
+      <c r="B369" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C369">
+        <v>4</v>
+      </c>
+      <c r="D369">
+        <v>368</v>
+      </c>
+      <c r="E369" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>88</v>
+      </c>
+      <c r="B370" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C370">
+        <v>5000</v>
+      </c>
+      <c r="D370">
+        <v>399</v>
+      </c>
+      <c r="E370" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>88</v>
+      </c>
+      <c r="B371" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C371">
+        <v>2000</v>
+      </c>
+      <c r="D371">
+        <v>516</v>
+      </c>
+      <c r="E371" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>88</v>
+      </c>
+      <c r="B372" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C372">
+        <v>511</v>
+      </c>
+      <c r="D372">
+        <v>744</v>
+      </c>
+      <c r="E372" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>88</v>
+      </c>
+      <c r="B373" s="1">
+        <v>46213</v>
+      </c>
+      <c r="C373">
+        <v>500</v>
+      </c>
+      <c r="D373">
+        <v>392</v>
+      </c>
+      <c r="E373" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>88</v>
+      </c>
+      <c r="B374" s="1">
+        <v>46212</v>
+      </c>
+      <c r="C374">
+        <v>5000</v>
+      </c>
+      <c r="D374">
+        <v>420</v>
+      </c>
+      <c r="E374" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>88</v>
+      </c>
+      <c r="B375" s="1">
+        <v>46210</v>
+      </c>
+      <c r="C375">
+        <v>2000</v>
+      </c>
+      <c r="D375">
+        <v>517</v>
+      </c>
+      <c r="E375" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>88</v>
+      </c>
+      <c r="B376" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C376">
+        <v>534</v>
+      </c>
+      <c r="D376">
+        <v>708</v>
+      </c>
+      <c r="E376" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>88</v>
+      </c>
+      <c r="B377" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C377">
         <v>4000</v>
       </c>
-      <c r="D368">
-        <v>393</v>
-      </c>
-      <c r="E368" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A369" t="s">
-        <v>88</v>
-      </c>
-      <c r="B369" s="1">
-        <v>46098</v>
-      </c>
-      <c r="C369">
+      <c r="D377">
+        <v>475</v>
+      </c>
+      <c r="E377" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>88</v>
+      </c>
+      <c r="B378" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C378">
+        <v>271</v>
+      </c>
+      <c r="D378">
+        <v>223</v>
+      </c>
+      <c r="E378" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>88</v>
+      </c>
+      <c r="B379" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C379">
         <v>4000</v>
       </c>
-      <c r="D369">
-        <v>507</v>
-      </c>
-      <c r="E369" t="s">
+      <c r="D379">
+        <v>516</v>
+      </c>
+      <c r="E379" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A370" t="s">
-        <v>88</v>
-      </c>
-      <c r="B370" s="1">
-        <v>46097</v>
-      </c>
-      <c r="C370">
-        <v>362</v>
-      </c>
-      <c r="D370">
-        <v>742</v>
-      </c>
-      <c r="E370" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A371" t="s">
-        <v>88</v>
-      </c>
-      <c r="B371" s="1">
-        <v>46086</v>
-      </c>
-      <c r="C371">
-        <v>250</v>
-      </c>
-      <c r="D371">
-        <v>429</v>
-      </c>
-      <c r="E371" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A372" t="s">
-        <v>88</v>
-      </c>
-      <c r="B372" s="1">
-        <v>46085</v>
-      </c>
-      <c r="C372">
-        <v>5500</v>
-      </c>
-      <c r="D372">
-        <v>397</v>
-      </c>
-      <c r="E372" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A373" t="s">
-        <v>88</v>
-      </c>
-      <c r="B373" s="1">
-        <v>46083</v>
-      </c>
-      <c r="C373">
-        <v>4000</v>
-      </c>
-      <c r="D373">
-        <v>508</v>
-      </c>
-      <c r="E373" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A374" t="s">
-        <v>88</v>
-      </c>
-      <c r="B374" s="1">
-        <v>46083</v>
-      </c>
-      <c r="C374">
-        <v>264</v>
-      </c>
-      <c r="D374">
-        <v>710</v>
-      </c>
-      <c r="E374" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A375" t="s">
-        <v>88</v>
-      </c>
-      <c r="B375" s="1">
-        <v>46073</v>
-      </c>
-      <c r="C375">
-        <v>4000</v>
-      </c>
-      <c r="D375">
-        <v>467</v>
-      </c>
-      <c r="E375" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A376" t="s">
-        <v>88</v>
-      </c>
-      <c r="B376" s="1">
-        <v>46072</v>
-      </c>
-      <c r="C376">
-        <v>391</v>
-      </c>
-      <c r="D376">
-        <v>169</v>
-      </c>
-      <c r="E376" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A377" t="s">
-        <v>88</v>
-      </c>
-      <c r="B377" s="1">
-        <v>46070</v>
-      </c>
-      <c r="C377">
-        <v>6000</v>
-      </c>
-      <c r="D377">
-        <v>508</v>
-      </c>
-      <c r="E377" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A378" t="s">
-        <v>88</v>
-      </c>
-      <c r="B378" s="1">
-        <v>46069</v>
-      </c>
-      <c r="C378">
-        <v>279</v>
-      </c>
-      <c r="D378">
-        <v>789</v>
-      </c>
-      <c r="E378" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A379" t="s">
-        <v>88</v>
-      </c>
-      <c r="B379" s="1">
-        <v>46059</v>
-      </c>
-      <c r="C379">
-        <v>8500</v>
-      </c>
-      <c r="D379">
-        <v>400</v>
-      </c>
-      <c r="E379" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>88</v>
       </c>
       <c r="B380" s="1">
-        <v>46056</v>
+        <v>46195</v>
       </c>
       <c r="C380">
-        <v>423</v>
+        <v>955</v>
       </c>
       <c r="D380">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="E380" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>88</v>
       </c>
       <c r="B381" s="1">
-        <v>46043</v>
+        <v>46170</v>
       </c>
       <c r="C381">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="D381">
-        <v>509</v>
+        <v>409</v>
       </c>
       <c r="E381" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>88</v>
+      </c>
+      <c r="B382" s="1">
+        <v>46169</v>
+      </c>
+      <c r="C382">
+        <v>3000</v>
+      </c>
+      <c r="D382">
+        <v>518</v>
+      </c>
+      <c r="E382" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A382" t="s">
-        <v>88</v>
-      </c>
-      <c r="B382" s="1">
-        <v>46042</v>
-      </c>
-      <c r="C382">
-        <v>681</v>
-      </c>
-      <c r="D382">
-        <v>746</v>
-      </c>
-      <c r="E382" t="s">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>88</v>
+      </c>
+      <c r="B383" s="1">
+        <v>46167</v>
+      </c>
+      <c r="C383">
+        <v>334</v>
+      </c>
+      <c r="D383">
+        <v>805</v>
+      </c>
+      <c r="E383" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A383" t="s">
-        <v>88</v>
-      </c>
-      <c r="B383" s="1">
-        <v>46029</v>
-      </c>
-      <c r="C383">
-        <v>8000</v>
-      </c>
-      <c r="D383">
-        <v>511</v>
-      </c>
-      <c r="E383" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>88</v>
       </c>
       <c r="B384" s="1">
-        <v>46027</v>
+        <v>46153</v>
       </c>
       <c r="C384">
-        <v>574</v>
+        <v>380</v>
       </c>
       <c r="D384">
-        <v>711</v>
+        <v>789</v>
       </c>
       <c r="E384" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>88</v>
       </c>
       <c r="B385" s="1">
-        <v>46008</v>
+        <v>46141</v>
       </c>
       <c r="C385">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="D385">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E385" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>88</v>
       </c>
       <c r="B386" s="1">
-        <v>46007</v>
+        <v>46140</v>
       </c>
       <c r="C386">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="D386">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E386" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>88</v>
       </c>
       <c r="B387" s="1">
-        <v>46006</v>
+        <v>46139</v>
       </c>
       <c r="C387">
-        <v>399</v>
+        <v>473</v>
       </c>
       <c r="D387">
-        <v>731</v>
+        <v>795</v>
       </c>
       <c r="E387" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>88</v>
       </c>
       <c r="B388" s="1">
-        <v>46002</v>
+        <v>46127</v>
       </c>
       <c r="C388">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="D388">
-        <v>476</v>
+        <v>419</v>
       </c>
       <c r="E388" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>88</v>
       </c>
       <c r="B389" s="1">
-        <v>46001</v>
+        <v>46126</v>
       </c>
       <c r="C389">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="D389">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E389" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>88</v>
       </c>
       <c r="B390" s="1">
-        <v>45999</v>
+        <v>46125</v>
       </c>
       <c r="C390">
-        <v>1123</v>
+        <v>324</v>
       </c>
       <c r="D390">
-        <v>729</v>
+        <v>786</v>
       </c>
       <c r="E390" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>88</v>
       </c>
       <c r="B391" s="1">
-        <v>45989</v>
+        <v>46114</v>
       </c>
       <c r="C391">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="D391">
-        <v>408</v>
+        <v>477</v>
       </c>
       <c r="E391" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>88</v>
       </c>
       <c r="B392" s="1">
-        <v>45987</v>
+        <v>46112</v>
       </c>
       <c r="C392">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="D392">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="E392" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>88</v>
       </c>
       <c r="B393" s="1">
-        <v>45986</v>
+        <v>46111</v>
       </c>
       <c r="C393">
-        <v>777</v>
+        <v>356</v>
       </c>
       <c r="D393">
-        <v>699</v>
+        <v>802</v>
       </c>
       <c r="E393" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>88</v>
       </c>
       <c r="B394" s="1">
-        <v>45975</v>
+        <v>46099</v>
       </c>
       <c r="C394">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="D394">
-        <v>462</v>
+        <v>393</v>
       </c>
       <c r="E394" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>88</v>
       </c>
       <c r="B395" s="1">
-        <v>45973</v>
+        <v>46098</v>
       </c>
       <c r="C395">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="D395">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="E395" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>88</v>
       </c>
       <c r="B396" s="1">
-        <v>45971</v>
+        <v>46097</v>
       </c>
       <c r="C396">
-        <v>714</v>
+        <v>362</v>
       </c>
       <c r="D396">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="E396" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>88</v>
       </c>
       <c r="B397" s="1">
-        <v>45959</v>
+        <v>46086</v>
       </c>
       <c r="C397">
+        <v>250</v>
+      </c>
+      <c r="D397">
+        <v>429</v>
+      </c>
+      <c r="E397" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>88</v>
+      </c>
+      <c r="B398" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C398">
+        <v>5500</v>
+      </c>
+      <c r="D398">
+        <v>397</v>
+      </c>
+      <c r="E398" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>88</v>
+      </c>
+      <c r="B399" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C399">
+        <v>4000</v>
+      </c>
+      <c r="D399">
+        <v>508</v>
+      </c>
+      <c r="E399" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>88</v>
+      </c>
+      <c r="B400" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C400">
+        <v>264</v>
+      </c>
+      <c r="D400">
+        <v>710</v>
+      </c>
+      <c r="E400" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>88</v>
+      </c>
+      <c r="B401" s="1">
+        <v>46073</v>
+      </c>
+      <c r="C401">
+        <v>4000</v>
+      </c>
+      <c r="D401">
+        <v>467</v>
+      </c>
+      <c r="E401" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>88</v>
+      </c>
+      <c r="B402" s="1">
+        <v>46072</v>
+      </c>
+      <c r="C402">
+        <v>391</v>
+      </c>
+      <c r="D402">
+        <v>169</v>
+      </c>
+      <c r="E402" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>88</v>
+      </c>
+      <c r="B403" s="1">
+        <v>46070</v>
+      </c>
+      <c r="C403">
         <v>6000</v>
       </c>
-      <c r="D397">
-        <v>416</v>
-      </c>
-      <c r="E397" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A398" t="s">
-        <v>88</v>
-      </c>
-      <c r="B398" s="1">
-        <v>45958</v>
-      </c>
-      <c r="C398">
-        <v>1000</v>
-      </c>
-      <c r="D398">
-        <v>533</v>
-      </c>
-      <c r="E398" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A399" t="s">
-        <v>88</v>
-      </c>
-      <c r="B399" s="1">
-        <v>45957</v>
-      </c>
-      <c r="C399">
-        <v>302</v>
-      </c>
-      <c r="D399">
-        <v>761</v>
-      </c>
-      <c r="E399" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A400" t="s">
-        <v>88</v>
-      </c>
-      <c r="B400" s="1">
-        <v>45945</v>
-      </c>
-      <c r="C400">
-        <v>2500</v>
-      </c>
-      <c r="D400">
-        <v>472</v>
-      </c>
-      <c r="E400" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A401" t="s">
-        <v>88</v>
-      </c>
-      <c r="B401" s="1">
-        <v>45944</v>
-      </c>
-      <c r="C401">
-        <v>345</v>
-      </c>
-      <c r="D401">
-        <v>778</v>
-      </c>
-      <c r="E401" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A402" t="s">
-        <v>88</v>
-      </c>
-      <c r="B402" s="1">
-        <v>45936</v>
-      </c>
-      <c r="C402">
-        <v>4500</v>
-      </c>
-      <c r="D402">
-        <v>432</v>
-      </c>
-      <c r="E402" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A403" t="s">
-        <v>88</v>
-      </c>
-      <c r="B403" s="1">
-        <v>45931</v>
-      </c>
-      <c r="C403">
-        <v>1000</v>
-      </c>
       <c r="D403">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="E403" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>88</v>
       </c>
       <c r="B404" s="1">
-        <v>45929</v>
+        <v>46069</v>
       </c>
       <c r="C404">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D404">
-        <v>855</v>
+        <v>789</v>
       </c>
       <c r="E404" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>88</v>
       </c>
       <c r="B405" s="1">
-        <v>45918</v>
+        <v>46059</v>
       </c>
       <c r="C405">
-        <v>1250</v>
+        <v>8500</v>
       </c>
       <c r="D405">
-        <v>505</v>
+        <v>400</v>
       </c>
       <c r="E405" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>88</v>
       </c>
       <c r="B406" s="1">
-        <v>45917</v>
+        <v>46056</v>
       </c>
       <c r="C406">
-        <v>2500</v>
+        <v>423</v>
       </c>
       <c r="D406">
-        <v>462</v>
+        <v>749</v>
       </c>
       <c r="E406" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>88</v>
       </c>
       <c r="B407" s="1">
-        <v>45915</v>
+        <v>46043</v>
       </c>
       <c r="C407">
-        <v>228</v>
+        <v>6000</v>
       </c>
       <c r="D407">
+        <v>509</v>
+      </c>
+      <c r="E407" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>88</v>
+      </c>
+      <c r="B408" s="1">
+        <v>46042</v>
+      </c>
+      <c r="C408">
+        <v>681</v>
+      </c>
+      <c r="D408">
         <v>746</v>
       </c>
-      <c r="E407" t="s">
+      <c r="E408" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A408" t="s">
-        <v>88</v>
-      </c>
-      <c r="B408" s="1">
-        <v>45904</v>
-      </c>
-      <c r="C408">
-        <v>4500</v>
-      </c>
-      <c r="D408">
-        <v>446</v>
-      </c>
-      <c r="E408" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>88</v>
       </c>
       <c r="B409" s="1">
-        <v>45903</v>
+        <v>46029</v>
       </c>
       <c r="C409">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="D409">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="E409" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>88</v>
       </c>
       <c r="B410" s="1">
-        <v>45902</v>
+        <v>46027</v>
       </c>
       <c r="C410">
-        <v>249</v>
+        <v>574</v>
       </c>
       <c r="D410">
-        <v>772</v>
+        <v>711</v>
       </c>
       <c r="E410" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>88</v>
       </c>
       <c r="B411" s="1">
-        <v>45888</v>
+        <v>46008</v>
       </c>
       <c r="C411">
-        <v>2500</v>
+        <v>6000</v>
       </c>
       <c r="D411">
-        <v>470</v>
+        <v>399</v>
       </c>
       <c r="E411" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>88</v>
       </c>
       <c r="B412" s="1">
-        <v>45887</v>
+        <v>46007</v>
       </c>
       <c r="C412">
-        <v>192</v>
+        <v>5000</v>
       </c>
       <c r="D412">
-        <v>800</v>
+        <v>515</v>
       </c>
       <c r="E412" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>88</v>
+      </c>
+      <c r="B413" s="1">
+        <v>46006</v>
+      </c>
+      <c r="C413">
+        <v>399</v>
+      </c>
+      <c r="D413">
+        <v>731</v>
+      </c>
+      <c r="E413" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A413" t="s">
-        <v>88</v>
-      </c>
-      <c r="B413" s="1">
-        <v>45877</v>
-      </c>
-      <c r="C413">
-        <v>2500</v>
-      </c>
-      <c r="D413">
-        <v>481</v>
-      </c>
-      <c r="E413" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>88</v>
       </c>
       <c r="B414" s="1">
-        <v>45876</v>
+        <v>46002</v>
       </c>
       <c r="C414">
         <v>1000</v>
       </c>
       <c r="D414">
-        <v>534</v>
+        <v>476</v>
       </c>
       <c r="E414" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>88</v>
+      </c>
+      <c r="B415" s="1">
+        <v>46001</v>
+      </c>
+      <c r="C415">
+        <v>6000</v>
+      </c>
+      <c r="D415">
+        <v>520</v>
+      </c>
+      <c r="E415" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A415" t="s">
-        <v>88</v>
-      </c>
-      <c r="B415" s="1">
-        <v>45875</v>
-      </c>
-      <c r="C415">
-        <v>225</v>
-      </c>
-      <c r="D415">
-        <v>739</v>
-      </c>
-      <c r="E415" t="s">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>88</v>
+      </c>
+      <c r="B416" s="1">
+        <v>45999</v>
+      </c>
+      <c r="C416">
+        <v>1123</v>
+      </c>
+      <c r="D416">
+        <v>729</v>
+      </c>
+      <c r="E416" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A416" t="s">
-        <v>88</v>
-      </c>
-      <c r="B416" s="1">
-        <v>45860</v>
-      </c>
-      <c r="C416">
-        <v>4000</v>
-      </c>
-      <c r="D416">
-        <v>475</v>
-      </c>
-      <c r="E416" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>88</v>
       </c>
       <c r="B417" s="1">
-        <v>45859</v>
+        <v>45989</v>
       </c>
       <c r="C417">
-        <v>202</v>
+        <v>6000</v>
       </c>
       <c r="D417">
-        <v>788</v>
+        <v>408</v>
       </c>
       <c r="E417" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>88</v>
       </c>
       <c r="B418" s="1">
-        <v>45846</v>
+        <v>45987</v>
       </c>
       <c r="C418">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="D418">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="E418" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>88</v>
       </c>
       <c r="B419" s="1">
-        <v>45845</v>
+        <v>45986</v>
       </c>
       <c r="C419">
-        <v>356</v>
+        <v>777</v>
       </c>
       <c r="D419">
-        <v>750</v>
+        <v>699</v>
       </c>
       <c r="E419" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>88</v>
       </c>
       <c r="B420" s="1">
-        <v>45834</v>
+        <v>45975</v>
       </c>
       <c r="C420">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D420">
-        <v>521</v>
+        <v>462</v>
       </c>
       <c r="E420" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>88</v>
+      </c>
+      <c r="B421" s="1">
+        <v>45973</v>
+      </c>
+      <c r="C421">
+        <v>1000</v>
+      </c>
+      <c r="D421">
+        <v>533</v>
+      </c>
+      <c r="E421" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A421" t="s">
-        <v>88</v>
-      </c>
-      <c r="B421" s="1">
-        <v>45831</v>
-      </c>
-      <c r="C421">
-        <v>503</v>
-      </c>
-      <c r="D421">
-        <v>742</v>
-      </c>
-      <c r="E421" t="s">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>88</v>
+      </c>
+      <c r="B422" s="1">
+        <v>45971</v>
+      </c>
+      <c r="C422">
+        <v>714</v>
+      </c>
+      <c r="D422">
+        <v>738</v>
+      </c>
+      <c r="E422" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A422" t="s">
-        <v>88</v>
-      </c>
-      <c r="B422" s="1">
-        <v>45820</v>
-      </c>
-      <c r="C422">
-        <v>3000</v>
-      </c>
-      <c r="D422">
-        <v>529</v>
-      </c>
-      <c r="E422" t="s">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>88</v>
+      </c>
+      <c r="B423" s="1">
+        <v>45959</v>
+      </c>
+      <c r="C423">
+        <v>6000</v>
+      </c>
+      <c r="D423">
+        <v>416</v>
+      </c>
+      <c r="E423" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>88</v>
+      </c>
+      <c r="B424" s="1">
+        <v>45958</v>
+      </c>
+      <c r="C424">
+        <v>1000</v>
+      </c>
+      <c r="D424">
+        <v>533</v>
+      </c>
+      <c r="E424" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A423" t="s">
-        <v>88</v>
-      </c>
-      <c r="B423" s="1">
-        <v>45818</v>
-      </c>
-      <c r="C423">
-        <v>125</v>
-      </c>
-      <c r="D423">
-        <v>784</v>
-      </c>
-      <c r="E423" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A424" t="s">
-        <v>88</v>
-      </c>
-      <c r="B424" s="1">
-        <v>45812</v>
-      </c>
-      <c r="C424">
-        <v>500</v>
-      </c>
-      <c r="D424">
-        <v>504</v>
-      </c>
-      <c r="E424" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>88</v>
       </c>
       <c r="B425" s="1">
-        <v>45810</v>
+        <v>45957</v>
       </c>
       <c r="C425">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="D425">
-        <v>726</v>
+        <v>761</v>
       </c>
       <c r="E425" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>88</v>
       </c>
       <c r="B426" s="1">
-        <v>45790</v>
+        <v>45945</v>
       </c>
       <c r="C426">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="D426">
-        <v>547</v>
+        <v>472</v>
       </c>
       <c r="E426" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>88</v>
       </c>
       <c r="B427" s="1">
-        <v>45789</v>
+        <v>45944</v>
       </c>
       <c r="C427">
-        <v>511</v>
+        <v>345</v>
       </c>
       <c r="D427">
-        <v>706</v>
+        <v>778</v>
       </c>
       <c r="E427" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>88</v>
       </c>
       <c r="B428" s="1">
-        <v>45779</v>
+        <v>45936</v>
       </c>
       <c r="C428">
-        <v>500</v>
+        <v>4500</v>
       </c>
       <c r="D428">
-        <v>510</v>
+        <v>432</v>
       </c>
       <c r="E428" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>88</v>
       </c>
       <c r="B429" s="1">
-        <v>45778</v>
+        <v>45931</v>
       </c>
       <c r="C429">
         <v>1000</v>
       </c>
       <c r="D429">
-        <v>479</v>
+        <v>534</v>
       </c>
       <c r="E429" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>88</v>
       </c>
       <c r="B430" s="1">
-        <v>45775</v>
+        <v>45929</v>
       </c>
       <c r="C430">
-        <v>421</v>
+        <v>291</v>
       </c>
       <c r="D430">
-        <v>727</v>
+        <v>855</v>
       </c>
       <c r="E430" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>88</v>
       </c>
       <c r="B431" s="1">
-        <v>45761</v>
+        <v>45918</v>
       </c>
       <c r="C431">
-        <v>825</v>
+        <v>1250</v>
       </c>
       <c r="D431">
-        <v>764</v>
+        <v>505</v>
       </c>
       <c r="E431" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>88</v>
       </c>
       <c r="B432" s="1">
-        <v>45737</v>
+        <v>45917</v>
       </c>
       <c r="C432">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="D432">
-        <v>379</v>
+        <v>462</v>
       </c>
       <c r="E432" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>88</v>
       </c>
       <c r="B433" s="1">
-        <v>45733</v>
+        <v>45915</v>
       </c>
       <c r="C433">
-        <v>536</v>
+        <v>228</v>
       </c>
       <c r="D433">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="E433" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>88</v>
       </c>
       <c r="B434" s="1">
-        <v>45722</v>
+        <v>45904</v>
       </c>
       <c r="C434">
         <v>4500</v>
       </c>
       <c r="D434">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="E434" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>88</v>
       </c>
       <c r="B435" s="1">
-        <v>45719</v>
+        <v>45903</v>
       </c>
       <c r="C435">
-        <v>725</v>
+        <v>1000</v>
       </c>
       <c r="D435">
-        <v>667</v>
+        <v>534</v>
       </c>
       <c r="E435" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>88</v>
       </c>
       <c r="B436" s="1">
-        <v>45707</v>
+        <v>45902</v>
       </c>
       <c r="C436">
-        <v>6500</v>
+        <v>249</v>
       </c>
       <c r="D436">
-        <v>428</v>
+        <v>772</v>
       </c>
       <c r="E436" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>88</v>
+      </c>
+      <c r="B437" s="1">
+        <v>45888</v>
+      </c>
+      <c r="C437">
+        <v>2500</v>
+      </c>
+      <c r="D437">
+        <v>470</v>
+      </c>
+      <c r="E437" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>88</v>
+      </c>
+      <c r="B438" s="1">
+        <v>45887</v>
+      </c>
+      <c r="C438">
+        <v>192</v>
+      </c>
+      <c r="D438">
+        <v>800</v>
+      </c>
+      <c r="E438" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>88</v>
+      </c>
+      <c r="B439" s="1">
+        <v>45877</v>
+      </c>
+      <c r="C439">
+        <v>2500</v>
+      </c>
+      <c r="D439">
+        <v>481</v>
+      </c>
+      <c r="E439" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A437" t="s">
-        <v>88</v>
-      </c>
-      <c r="B437" s="1">
-        <v>45705</v>
-      </c>
-      <c r="C437">
-        <v>646</v>
-      </c>
-      <c r="D437">
-        <v>750</v>
-      </c>
-      <c r="E437" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A438" t="s">
-        <v>88</v>
-      </c>
-      <c r="B438" s="1">
-        <v>45693</v>
-      </c>
-      <c r="C438">
-        <v>4000</v>
-      </c>
-      <c r="D438">
-        <v>521</v>
-      </c>
-      <c r="E438" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A439" t="s">
-        <v>88</v>
-      </c>
-      <c r="B439" s="1">
-        <v>45692</v>
-      </c>
-      <c r="C439">
-        <v>455</v>
-      </c>
-      <c r="D439">
-        <v>802</v>
-      </c>
-      <c r="E439" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>88</v>
       </c>
       <c r="B440" s="1">
-        <v>45680</v>
+        <v>45876</v>
       </c>
       <c r="C440">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="D440">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="E440" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>88</v>
       </c>
       <c r="B441" s="1">
-        <v>45665</v>
+        <v>45875</v>
       </c>
       <c r="C441">
-        <v>1350</v>
+        <v>225</v>
       </c>
       <c r="D441">
-        <v>542</v>
+        <v>739</v>
       </c>
       <c r="E441" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>88</v>
       </c>
       <c r="B442" s="1">
-        <v>45664</v>
+        <v>45860</v>
       </c>
       <c r="C442">
-        <v>471</v>
+        <v>4000</v>
       </c>
       <c r="D442">
-        <v>793</v>
+        <v>475</v>
       </c>
       <c r="E442" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>88</v>
       </c>
       <c r="B443" s="1">
-        <v>45642</v>
+        <v>45859</v>
       </c>
       <c r="C443">
-        <v>1085</v>
+        <v>202</v>
       </c>
       <c r="D443">
-        <v>727</v>
+        <v>788</v>
       </c>
       <c r="E443" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>88</v>
       </c>
       <c r="B444" s="1">
-        <v>45629</v>
+        <v>45846</v>
       </c>
       <c r="C444">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="D444">
-        <v>466</v>
+        <v>518</v>
       </c>
       <c r="E444" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>88</v>
       </c>
       <c r="B445" s="1">
-        <v>45628</v>
+        <v>45845</v>
       </c>
       <c r="C445">
-        <v>676</v>
+        <v>356</v>
       </c>
       <c r="D445">
-        <v>705</v>
+        <v>750</v>
       </c>
       <c r="E445" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>88</v>
       </c>
       <c r="B446" s="1">
-        <v>45616</v>
+        <v>45834</v>
       </c>
       <c r="C446">
         <v>3000</v>
       </c>
       <c r="D446">
-        <v>463</v>
+        <v>521</v>
       </c>
       <c r="E446" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>88</v>
       </c>
       <c r="B447" s="1">
-        <v>45615</v>
+        <v>45831</v>
       </c>
       <c r="C447">
-        <v>400</v>
+        <v>503</v>
       </c>
       <c r="D447">
-        <v>539</v>
+        <v>742</v>
       </c>
       <c r="E447" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>88</v>
+      </c>
+      <c r="B448" s="1">
+        <v>45820</v>
+      </c>
+      <c r="C448">
+        <v>3000</v>
+      </c>
+      <c r="D448">
+        <v>529</v>
+      </c>
+      <c r="E448" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A448" t="s">
-        <v>88</v>
-      </c>
-      <c r="B448" s="1">
-        <v>45614</v>
-      </c>
-      <c r="C448">
-        <v>174</v>
-      </c>
-      <c r="D448">
-        <v>816</v>
-      </c>
-      <c r="E448" t="s">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>88</v>
+      </c>
+      <c r="B449" s="1">
+        <v>45818</v>
+      </c>
+      <c r="C449">
+        <v>125</v>
+      </c>
+      <c r="D449">
+        <v>784</v>
+      </c>
+      <c r="E449" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A449" t="s">
-        <v>88</v>
-      </c>
-      <c r="B449" s="1">
-        <v>45611</v>
-      </c>
-      <c r="C449">
-        <v>800</v>
-      </c>
-      <c r="D449">
-        <v>478</v>
-      </c>
-      <c r="E449" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>88</v>
       </c>
       <c r="B450" s="1">
-        <v>45609</v>
+        <v>45812</v>
       </c>
       <c r="C450">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D450">
-        <v>547</v>
+        <v>504</v>
       </c>
       <c r="E450" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>88</v>
       </c>
       <c r="B451" s="1">
-        <v>45608</v>
+        <v>45810</v>
       </c>
       <c r="C451">
-        <v>733</v>
+        <v>277</v>
       </c>
       <c r="D451">
-        <v>812</v>
+        <v>726</v>
       </c>
       <c r="E451" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>88</v>
       </c>
       <c r="B452" s="1">
-        <v>45588</v>
+        <v>45790</v>
       </c>
       <c r="C452">
-        <v>1800</v>
+        <v>500</v>
       </c>
       <c r="D452">
-        <v>433</v>
+        <v>547</v>
       </c>
       <c r="E452" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>88</v>
       </c>
       <c r="B453" s="1">
-        <v>45587</v>
+        <v>45789</v>
       </c>
       <c r="C453">
-        <v>400</v>
+        <v>511</v>
       </c>
       <c r="D453">
-        <v>539</v>
+        <v>706</v>
       </c>
       <c r="E453" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>88</v>
       </c>
       <c r="B454" s="1">
-        <v>45586</v>
+        <v>45779</v>
       </c>
       <c r="C454">
-        <v>648</v>
+        <v>500</v>
       </c>
       <c r="D454">
-        <v>791</v>
+        <v>510</v>
       </c>
       <c r="E454" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>88</v>
       </c>
       <c r="B455" s="1">
-        <v>45575</v>
+        <v>45778</v>
       </c>
       <c r="C455">
         <v>1000</v>
       </c>
       <c r="D455">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="E455" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>88</v>
       </c>
       <c r="B456" s="1">
-        <v>45574</v>
+        <v>45775</v>
       </c>
       <c r="C456">
-        <v>500</v>
+        <v>421</v>
       </c>
       <c r="D456">
-        <v>539</v>
+        <v>727</v>
       </c>
       <c r="E456" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>88</v>
       </c>
       <c r="B457" s="1">
-        <v>45572</v>
+        <v>45761</v>
       </c>
       <c r="C457">
-        <v>1613</v>
+        <v>825</v>
       </c>
       <c r="D457">
-        <v>743</v>
+        <v>764</v>
       </c>
       <c r="E457" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>88</v>
       </c>
       <c r="B458" s="1">
-        <v>45554</v>
+        <v>45737</v>
       </c>
       <c r="C458">
+        <v>7500</v>
+      </c>
+      <c r="D458">
+        <v>379</v>
+      </c>
+      <c r="E458" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>88</v>
+      </c>
+      <c r="B459" s="1">
+        <v>45733</v>
+      </c>
+      <c r="C459">
+        <v>536</v>
+      </c>
+      <c r="D459">
+        <v>736</v>
+      </c>
+      <c r="E459" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>88</v>
+      </c>
+      <c r="B460" s="1">
+        <v>45722</v>
+      </c>
+      <c r="C460">
+        <v>4500</v>
+      </c>
+      <c r="D460">
+        <v>410</v>
+      </c>
+      <c r="E460" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>88</v>
+      </c>
+      <c r="B461" s="1">
+        <v>45719</v>
+      </c>
+      <c r="C461">
+        <v>725</v>
+      </c>
+      <c r="D461">
+        <v>667</v>
+      </c>
+      <c r="E461" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>88</v>
+      </c>
+      <c r="B462" s="1">
+        <v>45707</v>
+      </c>
+      <c r="C462">
+        <v>6500</v>
+      </c>
+      <c r="D462">
+        <v>428</v>
+      </c>
+      <c r="E462" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>88</v>
+      </c>
+      <c r="B463" s="1">
+        <v>45705</v>
+      </c>
+      <c r="C463">
+        <v>646</v>
+      </c>
+      <c r="D463">
+        <v>750</v>
+      </c>
+      <c r="E463" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>88</v>
+      </c>
+      <c r="B464" s="1">
+        <v>45693</v>
+      </c>
+      <c r="C464">
         <v>4000</v>
       </c>
-      <c r="D458">
-        <v>509</v>
-      </c>
-      <c r="E458" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A459" t="s">
-        <v>88</v>
-      </c>
-      <c r="B459" s="1">
-        <v>45548</v>
-      </c>
-      <c r="C459">
-        <v>1000</v>
-      </c>
-      <c r="D459">
-        <v>446</v>
-      </c>
-      <c r="E459" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A460" t="s">
-        <v>88</v>
-      </c>
-      <c r="B460" s="1">
-        <v>45544</v>
-      </c>
-      <c r="C460">
-        <v>911</v>
-      </c>
-      <c r="D460">
-        <v>732</v>
-      </c>
-      <c r="E460" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A461" t="s">
-        <v>88</v>
-      </c>
-      <c r="B461" s="1">
-        <v>45531</v>
-      </c>
-      <c r="C461">
-        <v>3300</v>
-      </c>
-      <c r="D461">
-        <v>507</v>
-      </c>
-      <c r="E461" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A462" t="s">
-        <v>88</v>
-      </c>
-      <c r="B462" s="1">
-        <v>45530</v>
-      </c>
-      <c r="C462">
-        <v>1121</v>
-      </c>
-      <c r="D462">
-        <v>694</v>
-      </c>
-      <c r="E462" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A463" t="s">
-        <v>88</v>
-      </c>
-      <c r="B463" s="1">
-        <v>45519</v>
-      </c>
-      <c r="C463">
-        <v>2000</v>
-      </c>
-      <c r="D463">
-        <v>394</v>
-      </c>
-      <c r="E463" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A464" t="s">
-        <v>88</v>
-      </c>
-      <c r="B464" s="1">
-        <v>45518</v>
-      </c>
-      <c r="C464">
-        <v>3200</v>
-      </c>
       <c r="D464">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="E464" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>88</v>
       </c>
       <c r="B465" s="1">
-        <v>45517</v>
+        <v>45692</v>
       </c>
       <c r="C465">
-        <v>763</v>
+        <v>455</v>
       </c>
       <c r="D465">
-        <v>690</v>
+        <v>802</v>
       </c>
       <c r="E465" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>88</v>
       </c>
       <c r="B466" s="1">
-        <v>45504</v>
+        <v>45680</v>
       </c>
       <c r="C466">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="D466">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="E466" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>88</v>
       </c>
       <c r="B467" s="1">
-        <v>45503</v>
+        <v>45665</v>
       </c>
       <c r="C467">
-        <v>964</v>
+        <v>1350</v>
       </c>
       <c r="D467">
-        <v>686</v>
+        <v>542</v>
       </c>
       <c r="E467" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>88</v>
+      </c>
+      <c r="B468" s="1">
+        <v>45664</v>
+      </c>
+      <c r="C468">
+        <v>471</v>
+      </c>
+      <c r="D468">
+        <v>793</v>
+      </c>
+      <c r="E468" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A468" t="s">
-        <v>88</v>
-      </c>
-      <c r="B468" s="1">
-        <v>45491</v>
-      </c>
-      <c r="C468">
-        <v>1800</v>
-      </c>
-      <c r="D468">
-        <v>400</v>
-      </c>
-      <c r="E468" t="s">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>88</v>
+      </c>
+      <c r="B469" s="1">
+        <v>45642</v>
+      </c>
+      <c r="C469">
+        <v>1085</v>
+      </c>
+      <c r="D469">
+        <v>727</v>
+      </c>
+      <c r="E469" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>88</v>
+      </c>
+      <c r="B470" s="1">
+        <v>45629</v>
+      </c>
+      <c r="C470">
+        <v>800</v>
+      </c>
+      <c r="D470">
+        <v>466</v>
+      </c>
+      <c r="E470" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A469" t="s">
-        <v>88</v>
-      </c>
-      <c r="B469" s="1">
-        <v>45490</v>
-      </c>
-      <c r="C469">
-        <v>6300</v>
-      </c>
-      <c r="D469">
-        <v>515</v>
-      </c>
-      <c r="E469" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A470" t="s">
-        <v>88</v>
-      </c>
-      <c r="B470" s="1">
-        <v>45489</v>
-      </c>
-      <c r="C470">
-        <v>1391</v>
-      </c>
-      <c r="D470">
-        <v>670</v>
-      </c>
-      <c r="E470" t="s">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>88</v>
+      </c>
+      <c r="B471" s="1">
+        <v>45628</v>
+      </c>
+      <c r="C471">
+        <v>676</v>
+      </c>
+      <c r="D471">
+        <v>705</v>
+      </c>
+      <c r="E471" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A471" t="s">
-        <v>88</v>
-      </c>
-      <c r="B471" s="1">
-        <v>45481</v>
-      </c>
-      <c r="C471">
-        <v>3200</v>
-      </c>
-      <c r="D471">
-        <v>420</v>
-      </c>
-      <c r="E471" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>88</v>
       </c>
       <c r="B472" s="1">
-        <v>45478</v>
+        <v>45616</v>
       </c>
       <c r="C472">
-        <v>3750</v>
+        <v>3000</v>
       </c>
       <c r="D472">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="E472" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>88</v>
       </c>
       <c r="B473" s="1">
-        <v>45477</v>
+        <v>45615</v>
       </c>
       <c r="C473">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="D473">
-        <v>436</v>
+        <v>539</v>
       </c>
       <c r="E473" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>88</v>
       </c>
       <c r="B474" s="1">
-        <v>45475</v>
+        <v>45614</v>
       </c>
       <c r="C474">
-        <v>920</v>
+        <v>174</v>
       </c>
       <c r="D474">
-        <v>739</v>
+        <v>816</v>
       </c>
       <c r="E474" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>88</v>
       </c>
       <c r="B475" s="1">
-        <v>45462</v>
+        <v>45611</v>
       </c>
       <c r="C475">
-        <v>1499</v>
+        <v>800</v>
       </c>
       <c r="D475">
-        <v>663</v>
+        <v>478</v>
       </c>
       <c r="E475" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>88</v>
       </c>
       <c r="B476" s="1">
-        <v>45443</v>
+        <v>45609</v>
       </c>
       <c r="C476">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="D476">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="E476" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>88</v>
       </c>
       <c r="B477" s="1">
-        <v>45442</v>
+        <v>45608</v>
       </c>
       <c r="C477">
-        <v>2985</v>
+        <v>733</v>
       </c>
       <c r="D477">
-        <v>676</v>
+        <v>812</v>
       </c>
       <c r="E477" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>88</v>
       </c>
       <c r="B478" s="1">
+        <v>45588</v>
+      </c>
+      <c r="C478">
+        <v>1800</v>
+      </c>
+      <c r="D478">
+        <v>433</v>
+      </c>
+      <c r="E478" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>88</v>
+      </c>
+      <c r="B479" s="1">
+        <v>45587</v>
+      </c>
+      <c r="C479">
+        <v>400</v>
+      </c>
+      <c r="D479">
+        <v>539</v>
+      </c>
+      <c r="E479" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>88</v>
+      </c>
+      <c r="B480" s="1">
+        <v>45586</v>
+      </c>
+      <c r="C480">
+        <v>648</v>
+      </c>
+      <c r="D480">
+        <v>791</v>
+      </c>
+      <c r="E480" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>88</v>
+      </c>
+      <c r="B481" s="1">
+        <v>45575</v>
+      </c>
+      <c r="C481">
+        <v>1000</v>
+      </c>
+      <c r="D481">
+        <v>444</v>
+      </c>
+      <c r="E481" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>88</v>
+      </c>
+      <c r="B482" s="1">
+        <v>45574</v>
+      </c>
+      <c r="C482">
+        <v>500</v>
+      </c>
+      <c r="D482">
+        <v>539</v>
+      </c>
+      <c r="E482" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>88</v>
+      </c>
+      <c r="B483" s="1">
+        <v>45572</v>
+      </c>
+      <c r="C483">
+        <v>1613</v>
+      </c>
+      <c r="D483">
+        <v>743</v>
+      </c>
+      <c r="E483" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>88</v>
+      </c>
+      <c r="B484" s="1">
+        <v>45554</v>
+      </c>
+      <c r="C484">
+        <v>4000</v>
+      </c>
+      <c r="D484">
+        <v>509</v>
+      </c>
+      <c r="E484" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>88</v>
+      </c>
+      <c r="B485" s="1">
+        <v>45548</v>
+      </c>
+      <c r="C485">
+        <v>1000</v>
+      </c>
+      <c r="D485">
+        <v>446</v>
+      </c>
+      <c r="E485" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>88</v>
+      </c>
+      <c r="B486" s="1">
+        <v>45544</v>
+      </c>
+      <c r="C486">
+        <v>911</v>
+      </c>
+      <c r="D486">
+        <v>732</v>
+      </c>
+      <c r="E486" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>88</v>
+      </c>
+      <c r="B487" s="1">
+        <v>45531</v>
+      </c>
+      <c r="C487">
+        <v>3300</v>
+      </c>
+      <c r="D487">
+        <v>507</v>
+      </c>
+      <c r="E487" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>88</v>
+      </c>
+      <c r="B488" s="1">
+        <v>45530</v>
+      </c>
+      <c r="C488">
+        <v>1121</v>
+      </c>
+      <c r="D488">
+        <v>694</v>
+      </c>
+      <c r="E488" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>88</v>
+      </c>
+      <c r="B489" s="1">
+        <v>45519</v>
+      </c>
+      <c r="C489">
+        <v>2000</v>
+      </c>
+      <c r="D489">
+        <v>394</v>
+      </c>
+      <c r="E489" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>88</v>
+      </c>
+      <c r="B490" s="1">
+        <v>45518</v>
+      </c>
+      <c r="C490">
+        <v>3200</v>
+      </c>
+      <c r="D490">
+        <v>509</v>
+      </c>
+      <c r="E490" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>88</v>
+      </c>
+      <c r="B491" s="1">
+        <v>45517</v>
+      </c>
+      <c r="C491">
+        <v>763</v>
+      </c>
+      <c r="D491">
+        <v>690</v>
+      </c>
+      <c r="E491" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>88</v>
+      </c>
+      <c r="B492" s="1">
+        <v>45504</v>
+      </c>
+      <c r="C492">
+        <v>5000</v>
+      </c>
+      <c r="D492">
+        <v>510</v>
+      </c>
+      <c r="E492" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>88</v>
+      </c>
+      <c r="B493" s="1">
+        <v>45503</v>
+      </c>
+      <c r="C493">
+        <v>964</v>
+      </c>
+      <c r="D493">
+        <v>686</v>
+      </c>
+      <c r="E493" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>88</v>
+      </c>
+      <c r="B494" s="1">
+        <v>45491</v>
+      </c>
+      <c r="C494">
+        <v>1800</v>
+      </c>
+      <c r="D494">
+        <v>400</v>
+      </c>
+      <c r="E494" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>88</v>
+      </c>
+      <c r="B495" s="1">
+        <v>45490</v>
+      </c>
+      <c r="C495">
+        <v>6300</v>
+      </c>
+      <c r="D495">
+        <v>515</v>
+      </c>
+      <c r="E495" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>88</v>
+      </c>
+      <c r="B496" s="1">
+        <v>45489</v>
+      </c>
+      <c r="C496">
+        <v>1391</v>
+      </c>
+      <c r="D496">
+        <v>670</v>
+      </c>
+      <c r="E496" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>88</v>
+      </c>
+      <c r="B497" s="1">
+        <v>45481</v>
+      </c>
+      <c r="C497">
+        <v>3200</v>
+      </c>
+      <c r="D497">
+        <v>420</v>
+      </c>
+      <c r="E497" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>88</v>
+      </c>
+      <c r="B498" s="1">
+        <v>45478</v>
+      </c>
+      <c r="C498">
+        <v>3750</v>
+      </c>
+      <c r="D498">
+        <v>445</v>
+      </c>
+      <c r="E498" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>88</v>
+      </c>
+      <c r="B499" s="1">
+        <v>45477</v>
+      </c>
+      <c r="C499">
+        <v>1800</v>
+      </c>
+      <c r="D499">
+        <v>436</v>
+      </c>
+      <c r="E499" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>88</v>
+      </c>
+      <c r="B500" s="1">
+        <v>45475</v>
+      </c>
+      <c r="C500">
+        <v>920</v>
+      </c>
+      <c r="D500">
+        <v>739</v>
+      </c>
+      <c r="E500" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>88</v>
+      </c>
+      <c r="B501" s="1">
+        <v>45462</v>
+      </c>
+      <c r="C501">
+        <v>1499</v>
+      </c>
+      <c r="D501">
+        <v>663</v>
+      </c>
+      <c r="E501" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>88</v>
+      </c>
+      <c r="B502" s="1">
+        <v>45443</v>
+      </c>
+      <c r="C502">
+        <v>3000</v>
+      </c>
+      <c r="D502">
+        <v>522</v>
+      </c>
+      <c r="E502" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>88</v>
+      </c>
+      <c r="B503" s="1">
+        <v>45442</v>
+      </c>
+      <c r="C503">
+        <v>2985</v>
+      </c>
+      <c r="D503">
+        <v>676</v>
+      </c>
+      <c r="E503" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>88</v>
+      </c>
+      <c r="B504" s="1">
         <v>45406</v>
       </c>
-      <c r="C478">
+      <c r="C504">
         <v>1400</v>
       </c>
-      <c r="D478">
+      <c r="D504">
         <v>410</v>
       </c>
-      <c r="E478" t="s">
+      <c r="E504" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A479" t="s">
-        <v>88</v>
-      </c>
-      <c r="B479" s="1">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>88</v>
+      </c>
+      <c r="B505" s="1">
         <v>45405</v>
       </c>
-      <c r="C479">
+      <c r="C505">
         <v>2095</v>
       </c>
-      <c r="D479">
+      <c r="D505">
         <v>529</v>
-      </c>
-      <c r="E479" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A480" t="s">
-        <v>88</v>
-      </c>
-      <c r="B480" s="1">
-        <v>45393</v>
-      </c>
-      <c r="C480">
-        <v>4500</v>
-      </c>
-      <c r="D480">
-        <v>491</v>
-      </c>
-      <c r="E480" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A481" t="s">
-        <v>88</v>
-      </c>
-      <c r="B481" s="1">
-        <v>45392</v>
-      </c>
-      <c r="C481">
-        <v>1280</v>
-      </c>
-      <c r="D481">
-        <v>549</v>
-      </c>
-      <c r="E481" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A482" t="s">
-        <v>88</v>
-      </c>
-      <c r="B482" s="1">
-        <v>45377</v>
-      </c>
-      <c r="C482">
-        <v>1500</v>
-      </c>
-      <c r="D482">
-        <v>388</v>
-      </c>
-      <c r="E482" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A483" t="s">
-        <v>88</v>
-      </c>
-      <c r="B483" s="1">
-        <v>45376</v>
-      </c>
-      <c r="C483">
-        <v>1980</v>
-      </c>
-      <c r="D483">
-        <v>524</v>
-      </c>
-      <c r="E483" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A484" t="s">
-        <v>88</v>
-      </c>
-      <c r="B484" s="1">
-        <v>45364</v>
-      </c>
-      <c r="C484">
-        <v>975</v>
-      </c>
-      <c r="D484">
-        <v>430</v>
-      </c>
-      <c r="E484" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A485" t="s">
-        <v>88</v>
-      </c>
-      <c r="B485" s="1">
-        <v>45363</v>
-      </c>
-      <c r="C485">
-        <v>2850</v>
-      </c>
-      <c r="D485">
-        <v>525</v>
-      </c>
-      <c r="E485" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A486" t="s">
-        <v>88</v>
-      </c>
-      <c r="B486" s="1">
-        <v>45351</v>
-      </c>
-      <c r="C486">
-        <v>2500</v>
-      </c>
-      <c r="D486">
-        <v>336</v>
-      </c>
-      <c r="E486" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A487" t="s">
-        <v>88</v>
-      </c>
-      <c r="B487" s="1">
-        <v>45350</v>
-      </c>
-      <c r="C487">
-        <v>1470</v>
-      </c>
-      <c r="D487">
-        <v>534</v>
-      </c>
-      <c r="E487" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A488" t="s">
-        <v>88</v>
-      </c>
-      <c r="B488" s="1">
-        <v>45338</v>
-      </c>
-      <c r="C488">
-        <v>150</v>
-      </c>
-      <c r="D488">
-        <v>437</v>
-      </c>
-      <c r="E488" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A489" t="s">
-        <v>88</v>
-      </c>
-      <c r="B489" s="1">
-        <v>45336</v>
-      </c>
-      <c r="C489">
-        <v>3500</v>
-      </c>
-      <c r="D489">
-        <v>422</v>
-      </c>
-      <c r="E489" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A490" t="s">
-        <v>88</v>
-      </c>
-      <c r="B490" s="1">
-        <v>45335</v>
-      </c>
-      <c r="C490">
-        <v>1490</v>
-      </c>
-      <c r="D490">
-        <v>535</v>
-      </c>
-      <c r="E490" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A491" t="s">
-        <v>88</v>
-      </c>
-      <c r="B491" s="1">
-        <v>45323</v>
-      </c>
-      <c r="C491">
-        <v>7000</v>
-      </c>
-      <c r="D491">
-        <v>365</v>
-      </c>
-      <c r="E491" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A492" t="s">
-        <v>88</v>
-      </c>
-      <c r="B492" s="1">
-        <v>45322</v>
-      </c>
-      <c r="C492">
-        <v>730</v>
-      </c>
-      <c r="D492">
-        <v>541</v>
-      </c>
-      <c r="E492" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A493" t="s">
-        <v>88</v>
-      </c>
-      <c r="B493" s="1">
-        <v>45314</v>
-      </c>
-      <c r="C493">
-        <v>1040</v>
-      </c>
-      <c r="D493">
-        <v>543</v>
-      </c>
-      <c r="E493" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A494" t="s">
-        <v>88</v>
-      </c>
-      <c r="B494" s="1">
-        <v>45301</v>
-      </c>
-      <c r="C494">
-        <v>1510</v>
-      </c>
-      <c r="D494">
-        <v>546</v>
-      </c>
-      <c r="E494" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A495" t="s">
-        <v>88</v>
-      </c>
-      <c r="B495" s="1">
-        <v>45281</v>
-      </c>
-      <c r="C495">
-        <v>400</v>
-      </c>
-      <c r="D495">
-        <v>386</v>
-      </c>
-      <c r="E495" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A496" t="s">
-        <v>88</v>
-      </c>
-      <c r="B496" s="1">
-        <v>45280</v>
-      </c>
-      <c r="C496">
-        <v>670</v>
-      </c>
-      <c r="D496">
-        <v>435</v>
-      </c>
-      <c r="E496" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A497" t="s">
-        <v>88</v>
-      </c>
-      <c r="B497" s="1">
-        <v>45279</v>
-      </c>
-      <c r="C497">
-        <v>1000</v>
-      </c>
-      <c r="D497">
-        <v>425</v>
-      </c>
-      <c r="E497" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A498" t="s">
-        <v>88</v>
-      </c>
-      <c r="B498" s="1">
-        <v>45278</v>
-      </c>
-      <c r="C498">
-        <v>1325</v>
-      </c>
-      <c r="D498">
-        <v>542</v>
-      </c>
-      <c r="E498" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A499" t="s">
-        <v>88</v>
-      </c>
-      <c r="B499" s="1">
-        <v>45268</v>
-      </c>
-      <c r="C499">
-        <v>5900</v>
-      </c>
-      <c r="D499">
-        <v>481</v>
-      </c>
-      <c r="E499" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A500" t="s">
-        <v>88</v>
-      </c>
-      <c r="B500" s="1">
-        <v>45267</v>
-      </c>
-      <c r="C500">
-        <v>1000</v>
-      </c>
-      <c r="D500">
-        <v>470</v>
-      </c>
-      <c r="E500" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A501" t="s">
-        <v>88</v>
-      </c>
-      <c r="B501" s="1">
-        <v>45266</v>
-      </c>
-      <c r="C501">
-        <v>4750</v>
-      </c>
-      <c r="D501">
-        <v>561</v>
-      </c>
-      <c r="E501" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A502" t="s">
-        <v>88</v>
-      </c>
-      <c r="B502" s="1">
-        <v>45225</v>
-      </c>
-      <c r="C502">
-        <v>3600</v>
-      </c>
-      <c r="D502">
-        <v>431</v>
-      </c>
-      <c r="E502" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A503" t="s">
-        <v>88</v>
-      </c>
-      <c r="B503" s="1">
-        <v>45224</v>
-      </c>
-      <c r="C503">
-        <v>300</v>
-      </c>
-      <c r="D503">
-        <v>486</v>
-      </c>
-      <c r="E503" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A504" t="s">
-        <v>88</v>
-      </c>
-      <c r="B504" s="1">
-        <v>45223</v>
-      </c>
-      <c r="C504">
-        <v>1548</v>
-      </c>
-      <c r="D504">
-        <v>776</v>
-      </c>
-      <c r="E504" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A505" t="s">
-        <v>88</v>
-      </c>
-      <c r="B505" s="1">
-        <v>45209</v>
-      </c>
-      <c r="C505">
-        <v>3725</v>
-      </c>
-      <c r="D505">
-        <v>500</v>
       </c>
       <c r="E505" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>88</v>
       </c>
       <c r="B506" s="1">
-        <v>45197</v>
+        <v>45393</v>
       </c>
       <c r="C506">
-        <v>600</v>
+        <v>4500</v>
       </c>
       <c r="D506">
-        <v>354</v>
+        <v>491</v>
       </c>
       <c r="E506" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>88</v>
       </c>
       <c r="B507" s="1">
-        <v>45196</v>
+        <v>45392</v>
       </c>
       <c r="C507">
-        <v>500</v>
+        <v>1280</v>
       </c>
       <c r="D507">
-        <v>472</v>
+        <v>549</v>
       </c>
       <c r="E507" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>88</v>
       </c>
       <c r="B508" s="1">
-        <v>45195</v>
+        <v>45377</v>
       </c>
       <c r="C508">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="D508">
-        <v>504</v>
+        <v>388</v>
       </c>
       <c r="E508" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>88</v>
+      </c>
+      <c r="B509" s="1">
+        <v>45376</v>
+      </c>
+      <c r="C509">
+        <v>1980</v>
+      </c>
+      <c r="D509">
+        <v>524</v>
+      </c>
+      <c r="E509" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A509" t="s">
-        <v>88</v>
-      </c>
-      <c r="B509" s="1">
-        <v>45189</v>
-      </c>
-      <c r="C509">
-        <v>1000</v>
-      </c>
-      <c r="D509">
-        <v>435</v>
-      </c>
-      <c r="E509" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>88</v>
       </c>
       <c r="B510" s="1">
-        <v>45188</v>
+        <v>45364</v>
       </c>
       <c r="C510">
-        <v>3200</v>
+        <v>975</v>
       </c>
       <c r="D510">
-        <v>531</v>
+        <v>430</v>
       </c>
       <c r="E510" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>88</v>
       </c>
       <c r="B511" s="1">
-        <v>45153</v>
+        <v>45363</v>
       </c>
       <c r="C511">
-        <v>4300</v>
+        <v>2850</v>
       </c>
       <c r="D511">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="E511" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>88</v>
       </c>
       <c r="B512" s="1">
-        <v>45141</v>
+        <v>45351</v>
       </c>
       <c r="C512">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="D512">
-        <v>388</v>
+        <v>336</v>
       </c>
       <c r="E512" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>88</v>
       </c>
       <c r="B513" s="1">
-        <v>45140</v>
+        <v>45350</v>
       </c>
       <c r="C513">
-        <v>800</v>
+        <v>1470</v>
       </c>
       <c r="D513">
-        <v>435</v>
+        <v>534</v>
       </c>
       <c r="E513" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>88</v>
       </c>
       <c r="B514" s="1">
-        <v>45139</v>
+        <v>45338</v>
       </c>
       <c r="C514">
-        <v>2000</v>
+        <v>150</v>
       </c>
       <c r="D514">
-        <v>517</v>
+        <v>437</v>
       </c>
       <c r="E514" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>88</v>
       </c>
       <c r="B515" s="1">
-        <v>45119</v>
+        <v>45336</v>
       </c>
       <c r="C515">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="D515">
-        <v>375</v>
+        <v>422</v>
       </c>
       <c r="E515" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>88</v>
       </c>
       <c r="B516" s="1">
-        <v>45118</v>
+        <v>45335</v>
       </c>
       <c r="C516">
-        <v>800</v>
+        <v>1490</v>
       </c>
       <c r="D516">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="E516" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>88</v>
       </c>
       <c r="B517" s="1">
-        <v>45114</v>
+        <v>45323</v>
       </c>
       <c r="C517">
-        <v>2300</v>
+        <v>7000</v>
       </c>
       <c r="D517">
-        <v>439</v>
+        <v>365</v>
       </c>
       <c r="E517" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>88</v>
       </c>
       <c r="B518" s="1">
-        <v>45113</v>
+        <v>45322</v>
       </c>
       <c r="C518">
-        <v>1500</v>
+        <v>730</v>
       </c>
       <c r="D518">
-        <v>463</v>
+        <v>541</v>
       </c>
       <c r="E518" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>88</v>
       </c>
       <c r="B519" s="1">
-        <v>45112</v>
+        <v>45314</v>
       </c>
       <c r="C519">
-        <v>500</v>
+        <v>1040</v>
       </c>
       <c r="D519">
-        <v>486</v>
+        <v>543</v>
       </c>
       <c r="E519" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>88</v>
       </c>
       <c r="B520" s="1">
-        <v>45111</v>
+        <v>45301</v>
       </c>
       <c r="C520">
-        <v>700</v>
+        <v>1510</v>
       </c>
       <c r="D520">
-        <v>511</v>
+        <v>546</v>
       </c>
       <c r="E520" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>88</v>
       </c>
       <c r="B521" s="1">
-        <v>45105</v>
+        <v>45281</v>
       </c>
       <c r="C521">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="D521">
-        <v>476</v>
+        <v>386</v>
       </c>
       <c r="E521" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>88</v>
       </c>
       <c r="B522" s="1">
-        <v>45104</v>
+        <v>45280</v>
       </c>
       <c r="C522">
-        <v>4300</v>
+        <v>670</v>
       </c>
       <c r="D522">
-        <v>486</v>
+        <v>435</v>
       </c>
       <c r="E522" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>88</v>
       </c>
       <c r="B523" s="1">
-        <v>45085</v>
+        <v>45279</v>
       </c>
       <c r="C523">
-        <v>4800</v>
+        <v>1000</v>
       </c>
       <c r="D523">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="E523" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>88</v>
       </c>
       <c r="B524" s="1">
-        <v>45070</v>
+        <v>45278</v>
       </c>
       <c r="C524">
-        <v>4800</v>
+        <v>1325</v>
       </c>
       <c r="D524">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="E524" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>88</v>
       </c>
       <c r="B525" s="1">
-        <v>45056</v>
+        <v>45268</v>
       </c>
       <c r="C525">
-        <v>589</v>
+        <v>5900</v>
       </c>
       <c r="D525">
-        <v>691</v>
+        <v>481</v>
       </c>
       <c r="E525" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>88</v>
       </c>
       <c r="B526" s="1">
-        <v>45042</v>
+        <v>45267</v>
       </c>
       <c r="C526">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="D526">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="E526" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>88</v>
       </c>
       <c r="B527" s="1">
-        <v>45028</v>
+        <v>45266</v>
       </c>
       <c r="C527">
-        <v>3500</v>
+        <v>4750</v>
       </c>
       <c r="D527">
-        <v>486</v>
+        <v>561</v>
       </c>
       <c r="E527" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>88</v>
       </c>
       <c r="B528" s="1">
-        <v>45014</v>
+        <v>45225</v>
       </c>
       <c r="C528">
-        <v>7000</v>
+        <v>3600</v>
       </c>
       <c r="D528">
-        <v>481</v>
+        <v>431</v>
       </c>
       <c r="E528" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>88</v>
+      </c>
+      <c r="B529" s="1">
+        <v>45224</v>
+      </c>
+      <c r="C529">
+        <v>300</v>
+      </c>
+      <c r="D529">
+        <v>486</v>
+      </c>
+      <c r="E529" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>88</v>
+      </c>
+      <c r="B530" s="1">
+        <v>45223</v>
+      </c>
+      <c r="C530">
+        <v>1548</v>
+      </c>
+      <c r="D530">
+        <v>776</v>
+      </c>
+      <c r="E530" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>88</v>
+      </c>
+      <c r="B531" s="1">
+        <v>45209</v>
+      </c>
+      <c r="C531">
+        <v>3725</v>
+      </c>
+      <c r="D531">
+        <v>500</v>
+      </c>
+      <c r="E531" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A529" t="s">
-        <v>88</v>
-      </c>
-      <c r="B529" s="1">
-        <v>45008</v>
-      </c>
-      <c r="C529">
-        <v>7000</v>
-      </c>
-      <c r="D529">
-        <v>484</v>
-      </c>
-      <c r="E529" t="s">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>88</v>
+      </c>
+      <c r="B532" s="1">
+        <v>45197</v>
+      </c>
+      <c r="C532">
+        <v>600</v>
+      </c>
+      <c r="D532">
+        <v>354</v>
+      </c>
+      <c r="E532" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>88</v>
+      </c>
+      <c r="B533" s="1">
+        <v>45196</v>
+      </c>
+      <c r="C533">
+        <v>500</v>
+      </c>
+      <c r="D533">
+        <v>472</v>
+      </c>
+      <c r="E533" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>88</v>
+      </c>
+      <c r="B534" s="1">
+        <v>45195</v>
+      </c>
+      <c r="C534">
+        <v>3000</v>
+      </c>
+      <c r="D534">
+        <v>504</v>
+      </c>
+      <c r="E534" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A530" t="s">
-        <v>88</v>
-      </c>
-      <c r="B530" s="1">
-        <v>45000</v>
-      </c>
-      <c r="C530">
-        <v>7000</v>
-      </c>
-      <c r="D530">
-        <v>490</v>
-      </c>
-      <c r="E530" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A531" t="s">
-        <v>88</v>
-      </c>
-      <c r="B531" s="1">
-        <v>44986</v>
-      </c>
-      <c r="C531">
-        <v>667</v>
-      </c>
-      <c r="D531">
-        <v>748</v>
-      </c>
-      <c r="E531" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A532" t="s">
-        <v>88</v>
-      </c>
-      <c r="B532" s="1">
-        <v>44972</v>
-      </c>
-      <c r="C532">
-        <v>699</v>
-      </c>
-      <c r="D532">
-        <v>791</v>
-      </c>
-      <c r="E532" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A533" t="s">
-        <v>88</v>
-      </c>
-      <c r="B533" s="1">
-        <v>44959</v>
-      </c>
-      <c r="C533">
-        <v>3300</v>
-      </c>
-      <c r="D533">
-        <v>489</v>
-      </c>
-      <c r="E533" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A534" t="s">
-        <v>88</v>
-      </c>
-      <c r="B534" s="1">
-        <v>44958</v>
-      </c>
-      <c r="C534">
-        <v>893</v>
-      </c>
-      <c r="D534">
-        <v>733</v>
-      </c>
-      <c r="E534" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>88</v>
       </c>
       <c r="B535" s="1">
-        <v>44944</v>
+        <v>45189</v>
       </c>
       <c r="C535">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="D535">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="E535" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>88</v>
       </c>
       <c r="B536" s="1">
-        <v>44937</v>
+        <v>45188</v>
       </c>
       <c r="C536">
-        <v>5500</v>
+        <v>3200</v>
       </c>
       <c r="D536">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="E536" t="s">
         <v>87</v>
       </c>
     </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>88</v>
+      </c>
+      <c r="B537" s="1">
+        <v>45153</v>
+      </c>
+      <c r="C537">
+        <v>4300</v>
+      </c>
+      <c r="D537">
+        <v>496</v>
+      </c>
+      <c r="E537" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>88</v>
+      </c>
+      <c r="B538" s="1">
+        <v>45141</v>
+      </c>
+      <c r="C538">
+        <v>1500</v>
+      </c>
+      <c r="D538">
+        <v>388</v>
+      </c>
+      <c r="E538" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>88</v>
+      </c>
+      <c r="B539" s="1">
+        <v>45140</v>
+      </c>
+      <c r="C539">
+        <v>800</v>
+      </c>
+      <c r="D539">
+        <v>435</v>
+      </c>
+      <c r="E539" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>88</v>
+      </c>
+      <c r="B540" s="1">
+        <v>45139</v>
+      </c>
+      <c r="C540">
+        <v>2000</v>
+      </c>
+      <c r="D540">
+        <v>517</v>
+      </c>
+      <c r="E540" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>88</v>
+      </c>
+      <c r="B541" s="1">
+        <v>45119</v>
+      </c>
+      <c r="C541">
+        <v>3800</v>
+      </c>
+      <c r="D541">
+        <v>375</v>
+      </c>
+      <c r="E541" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>88</v>
+      </c>
+      <c r="B542" s="1">
+        <v>45118</v>
+      </c>
+      <c r="C542">
+        <v>800</v>
+      </c>
+      <c r="D542">
+        <v>505</v>
+      </c>
+      <c r="E542" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>88</v>
+      </c>
+      <c r="B543" s="1">
+        <v>45114</v>
+      </c>
+      <c r="C543">
+        <v>2300</v>
+      </c>
+      <c r="D543">
+        <v>439</v>
+      </c>
+      <c r="E543" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>88</v>
+      </c>
+      <c r="B544" s="1">
+        <v>45113</v>
+      </c>
+      <c r="C544">
+        <v>1500</v>
+      </c>
+      <c r="D544">
+        <v>463</v>
+      </c>
+      <c r="E544" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>88</v>
+      </c>
+      <c r="B545" s="1">
+        <v>45112</v>
+      </c>
+      <c r="C545">
+        <v>500</v>
+      </c>
+      <c r="D545">
+        <v>486</v>
+      </c>
+      <c r="E545" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>88</v>
+      </c>
+      <c r="B546" s="1">
+        <v>45111</v>
+      </c>
+      <c r="C546">
+        <v>700</v>
+      </c>
+      <c r="D546">
+        <v>511</v>
+      </c>
+      <c r="E546" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>88</v>
+      </c>
+      <c r="B547" s="1">
+        <v>45105</v>
+      </c>
+      <c r="C547">
+        <v>500</v>
+      </c>
+      <c r="D547">
+        <v>476</v>
+      </c>
+      <c r="E547" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>88</v>
+      </c>
+      <c r="B548" s="1">
+        <v>45104</v>
+      </c>
+      <c r="C548">
+        <v>4300</v>
+      </c>
+      <c r="D548">
+        <v>486</v>
+      </c>
+      <c r="E548" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>88</v>
+      </c>
+      <c r="B549" s="1">
+        <v>45085</v>
+      </c>
+      <c r="C549">
+        <v>4800</v>
+      </c>
+      <c r="D549">
+        <v>486</v>
+      </c>
+      <c r="E549" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>88</v>
+      </c>
+      <c r="B550" s="1">
+        <v>45070</v>
+      </c>
+      <c r="C550">
+        <v>4800</v>
+      </c>
+      <c r="D550">
+        <v>486</v>
+      </c>
+      <c r="E550" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>88</v>
+      </c>
+      <c r="B551" s="1">
+        <v>45056</v>
+      </c>
+      <c r="C551">
+        <v>589</v>
+      </c>
+      <c r="D551">
+        <v>691</v>
+      </c>
+      <c r="E551" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>88</v>
+      </c>
+      <c r="B552" s="1">
+        <v>45042</v>
+      </c>
+      <c r="C552">
+        <v>3500</v>
+      </c>
+      <c r="D552">
+        <v>483</v>
+      </c>
+      <c r="E552" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>88</v>
+      </c>
+      <c r="B553" s="1">
+        <v>45028</v>
+      </c>
+      <c r="C553">
+        <v>3500</v>
+      </c>
+      <c r="D553">
+        <v>486</v>
+      </c>
+      <c r="E553" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>88</v>
+      </c>
+      <c r="B554" s="1">
+        <v>45014</v>
+      </c>
+      <c r="C554">
+        <v>7000</v>
+      </c>
+      <c r="D554">
+        <v>481</v>
+      </c>
+      <c r="E554" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>88</v>
+      </c>
+      <c r="B555" s="1">
+        <v>45008</v>
+      </c>
+      <c r="C555">
+        <v>7000</v>
+      </c>
+      <c r="D555">
+        <v>484</v>
+      </c>
+      <c r="E555" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>88</v>
+      </c>
+      <c r="B556" s="1">
+        <v>45000</v>
+      </c>
+      <c r="C556">
+        <v>7000</v>
+      </c>
+      <c r="D556">
+        <v>490</v>
+      </c>
+      <c r="E556" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>88</v>
+      </c>
+      <c r="B557" s="1">
+        <v>44986</v>
+      </c>
+      <c r="C557">
+        <v>667</v>
+      </c>
+      <c r="D557">
+        <v>748</v>
+      </c>
+      <c r="E557" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>88</v>
+      </c>
+      <c r="B558" s="1">
+        <v>44972</v>
+      </c>
+      <c r="C558">
+        <v>699</v>
+      </c>
+      <c r="D558">
+        <v>791</v>
+      </c>
+      <c r="E558" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>88</v>
+      </c>
+      <c r="B559" s="1">
+        <v>44959</v>
+      </c>
+      <c r="C559">
+        <v>3300</v>
+      </c>
+      <c r="D559">
+        <v>489</v>
+      </c>
+      <c r="E559" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>88</v>
+      </c>
+      <c r="B560" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C560">
+        <v>893</v>
+      </c>
+      <c r="D560">
+        <v>733</v>
+      </c>
+      <c r="E560" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>88</v>
+      </c>
+      <c r="B561" s="1">
+        <v>44944</v>
+      </c>
+      <c r="C561">
+        <v>5500</v>
+      </c>
+      <c r="D561">
+        <v>490</v>
+      </c>
+      <c r="E561" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>88</v>
+      </c>
+      <c r="B562" s="1">
+        <v>44937</v>
+      </c>
+      <c r="C562">
+        <v>5500</v>
+      </c>
+      <c r="D562">
+        <v>507</v>
+      </c>
+      <c r="E562" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E536" xr:uid="{F2A0282E-C66F-47D3-9A9F-ADD17816EADE}"/>
+  <autoFilter ref="A1:E562" xr:uid="{F2A0282E-C66F-47D3-9A9F-ADD17816EADE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
